--- a/kaggle_results/T11-06-2025/results_v209.xlsx
+++ b/kaggle_results/T11-06-2025/results_v209.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.git_projs\MedicalQA\kaggle_results\T11-06-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CF6AFC-AAC7-463B-83EE-AB7BAE8F3F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7F7731-BF18-4BDE-AACC-CFCDFA3F5E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4149,7 +4149,7 @@
         <v>-2.8600000000000014E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="5" customFormat="1" ht="322" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" s="5" customFormat="1" ht="350" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -4159,7 +4159,7 @@
       <c r="C7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="364" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>

--- a/kaggle_results/T11-06-2025/results_v209.xlsx
+++ b/kaggle_results/T11-06-2025/results_v209.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.git_projs\MedicalQA\kaggle_results\T11-06-2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Apps\obsidian\Research\1.git_projs\MedicalQA\kaggle_results\T11-06-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7F7731-BF18-4BDE-AACC-CFCDFA3F5E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133F93CF-87FD-44A9-9136-0831AE600D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2069,12 +2069,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L51"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="2" customFormat="1" ht="322" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" s="2" customFormat="1" ht="299.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>29</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>-0.11109999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>22</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>-9.4999999999999973E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>44</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>-6.700000000000006E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>-4.9800000000000011E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>33</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>-4.5800000000000063E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2685,7 +2685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>4</v>
       </c>
@@ -2721,7 +2721,7 @@
         <v>-2.8600000000000014E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>7</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>-7.5000000000000622E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>17</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>-4.7000000000000375E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>40</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>3.3000000000000029E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>48</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>4.049999999999998E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>27</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>24</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>7.2199999999999931E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>11</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>0.1754</v>
       </c>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>25</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>0.30640000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>41</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>42</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>13</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>0.35249999999999992</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>43</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>0.36680000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>45</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>46</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>16</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>0.57479999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>0.7228</v>
       </c>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>49</v>
       </c>
@@ -3927,13 +3927,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96768507-BC44-44FA-BBBE-68831BBA3309}">
   <dimension ref="A1:L51"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="53" customWidth="1"/>
     <col min="5" max="5" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -4076,7 +4076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -4149,7 +4149,7 @@
         <v>-2.8600000000000014E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="5" customFormat="1" ht="350" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" s="5" customFormat="1" ht="371.25" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>-4.9800000000000011E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>-7.5000000000000622E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -4365,7 +4365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="285" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
@@ -4375,10 +4375,10 @@
       <c r="C13" t="s">
         <v>74</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="4" t="s">
         <v>76</v>
       </c>
       <c r="F13" t="s">
@@ -4401,7 +4401,7 @@
         <v>0.1754</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>0.35249999999999992</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="364" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="371.25" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>0.57479999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>-4.7000000000000375E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
@@ -4725,7 +4725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>-9.4999999999999973E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>24</v>
       </c>
@@ -4869,7 +4869,7 @@
         <v>7.2199999999999931E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>25</v>
       </c>
@@ -4905,7 +4905,7 @@
         <v>0.30640000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>26</v>
       </c>
@@ -4941,7 +4941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>27</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>28</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>-0.11109999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>30</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31</v>
       </c>
@@ -5122,7 +5122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>32</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>33</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>-4.5800000000000063E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>34</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>35</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>36</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>37</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>38</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <v>39</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>40</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>3.3000000000000029E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>41</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>42</v>
       </c>
@@ -5518,7 +5518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>43</v>
       </c>
@@ -5554,7 +5554,7 @@
         <v>0.36680000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>44</v>
       </c>
@@ -5590,7 +5590,7 @@
         <v>-6.700000000000006E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>45</v>
       </c>
@@ -5626,7 +5626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="5" customFormat="1" ht="238" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" s="5" customFormat="1" ht="243" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>46</v>
       </c>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="245" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="245.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>47</v>
       </c>
@@ -5672,7 +5672,7 @@
       <c r="C49" t="s">
         <v>284</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="4" t="s">
         <v>285</v>
       </c>
       <c r="E49" s="4" t="s">
@@ -5698,7 +5698,7 @@
         <v>0.7228</v>
       </c>
     </row>
-    <row r="50" spans="1:12" s="5" customFormat="1" ht="182" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" s="5" customFormat="1" ht="186" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>48</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>4.049999999999998E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>49</v>
       </c>
